--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.5902,0.3060,0.0992,0.0486</t>
-  </si>
-  <si>
-    <t>0.0156,0.0026,0.0004,0.9937</t>
-  </si>
-  <si>
-    <t>0.2643,0.2364,0.0123,0.5077</t>
-  </si>
-  <si>
-    <t>0.0527,0.0269,0.0055,0.9667</t>
-  </si>
-  <si>
-    <t>0.9946,0.0017,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9941,0.0029,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9807,0.0089,0.0034,0.0020</t>
-  </si>
-  <si>
-    <t>0.9819,0.0012,0.0025,0.0072</t>
-  </si>
-  <si>
-    <t>0.9861,0.0136,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9598,0.0652,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9911,0.0025,0.0003,0.0018</t>
-  </si>
-  <si>
-    <t>0.9943,0.0028,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.4336,0.1077,0.5718,0.0218</t>
-  </si>
-  <si>
-    <t>0.1182,0.0465,0.8869,0.0041</t>
-  </si>
-  <si>
-    <t>0.2528,0.0067,0.8637,0.0013</t>
-  </si>
-  <si>
-    <t>0.1160,0.0422,0.8954,0.0036</t>
-  </si>
-  <si>
-    <t>0.8093,0.0613,0.1098,0.0158</t>
-  </si>
-  <si>
-    <t>0.0172,0.9767,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.0905,0.9467,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.6404,0.4628,0.0106,0.0062</t>
-  </si>
-  <si>
-    <t>0.0734,0.9405,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.0103,0.9865,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.3663,0.0071,0.8075,0.0023</t>
-  </si>
-  <si>
-    <t>0.4595,0.0734,0.2162,0.3660</t>
-  </si>
-  <si>
-    <t>0.0045,0.0049,0.9854,0.0060</t>
-  </si>
-  <si>
-    <t>0.4858,0.0217,0.4989,0.0716</t>
-  </si>
-  <si>
-    <t>0.1966,0.0085,0.8802,0.0019</t>
-  </si>
-  <si>
-    <t>0.0100,0.0021,0.9693,0.0124</t>
-  </si>
-  <si>
-    <t>0.0008,0.0015,0.9872,0.0279</t>
-  </si>
-  <si>
-    <t>0.5069,0.6688,0.0039,0.0027</t>
-  </si>
-  <si>
-    <t>0.1157,0.5754,0.4270,0.0060</t>
-  </si>
-  <si>
-    <t>0.0040,0.0528,0.9861,0.0001</t>
-  </si>
-  <si>
-    <t>0.0125,0.9546,0.0139,0.0002</t>
-  </si>
-  <si>
-    <t>0.5975,0.3826,0.0704,0.0215</t>
-  </si>
-  <si>
-    <t>0.7621,0.1679,0.0724,0.0039</t>
-  </si>
-  <si>
-    <t>0.7817,0.3564,0.0083,0.0027</t>
-  </si>
-  <si>
-    <t>0.0039,0.9853,0.0303,0.0021</t>
-  </si>
-  <si>
-    <t>0.0085,0.6914,0.2370,0.1811</t>
-  </si>
-  <si>
-    <t>0.0239,0.0545,0.9531,0.0065</t>
-  </si>
-  <si>
-    <t>0.0350,0.4950,0.7171,0.0079</t>
-  </si>
-  <si>
-    <t>0.3396,0.0117,0.7633,0.0098</t>
-  </si>
-  <si>
-    <t>0.0208,0.0685,0.9486,0.0016</t>
-  </si>
-  <si>
-    <t>0.0015,0.9925,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0276,0.1903,0.8984,0.0064</t>
-  </si>
-  <si>
-    <t>0.0543,0.7370,0.0230,0.6174</t>
-  </si>
-  <si>
-    <t>0.0013,0.9839,0.0215,0.0316</t>
-  </si>
-  <si>
-    <t>0.0020,0.9900,0.0519,0.0005</t>
-  </si>
-  <si>
-    <t>0.0018,0.9845,0.0383,0.0099</t>
-  </si>
-  <si>
-    <t>0.0004,0.2317,0.9850,0.0031</t>
-  </si>
-  <si>
-    <t>0.0008,0.3957,0.9915,0.0002</t>
-  </si>
-  <si>
-    <t>0.0324,0.0192,0.9617,0.0037</t>
-  </si>
-  <si>
-    <t>0.0201,0.0051,0.9486,0.0270</t>
-  </si>
-  <si>
-    <t>0.0038,0.0648,0.9800,0.0041</t>
-  </si>
-  <si>
-    <t>0.0110,0.0119,0.9678,0.0091</t>
-  </si>
-  <si>
-    <t>0.9249,0.0960,0.0077,0.0015</t>
-  </si>
-  <si>
-    <t>0.9571,0.0386,0.0139,0.0026</t>
-  </si>
-  <si>
-    <t>0.9137,0.1072,0.0090,0.0032</t>
-  </si>
-  <si>
-    <t>0.0095,0.0449,0.9712,0.0021</t>
-  </si>
-  <si>
-    <t>0.9658,0.0179,0.0041,0.0037</t>
-  </si>
-  <si>
-    <t>0.9797,0.0144,0.0048,0.0008</t>
-  </si>
-  <si>
-    <t>0.9015,0.1683,0.0047,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.8766,0.9514,0.0004</t>
-  </si>
-  <si>
-    <t>0.0028,0.0561,0.9832,0.0029</t>
-  </si>
-  <si>
-    <t>0.0159,0.0958,0.9596,0.0015</t>
-  </si>
-  <si>
-    <t>0.0004,0.9132,0.9723,0.0001</t>
-  </si>
-  <si>
-    <t>0.0099,0.0549,0.9793,0.0007</t>
-  </si>
-  <si>
-    <t>0.0223,0.9186,0.0675,0.0019</t>
-  </si>
-  <si>
-    <t>0.0047,0.9938,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.8744,0.0370,0.0732,0.0097</t>
-  </si>
-  <si>
-    <t>0.8765,0.0336,0.0777,0.0167</t>
-  </si>
-  <si>
-    <t>0.0242,0.0230,0.9691,0.0036</t>
-  </si>
-  <si>
-    <t>0.0013,0.9277,0.7718,0.0004</t>
-  </si>
-  <si>
-    <t>0.0010,0.9000,0.7805,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9926,0.0617,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.9493,0.3889,0.0002</t>
-  </si>
-  <si>
-    <t>0.0984,0.0010,0.0060,0.9481</t>
-  </si>
-  <si>
-    <t>0.0018,0.0001,0.0003,0.9989</t>
-  </si>
-  <si>
-    <t>0.0012,0.0328,0.0010,0.9973</t>
-  </si>
-  <si>
-    <t>0.0335,0.0213,0.0861,0.9449</t>
-  </si>
-  <si>
-    <t>0.0088,0.0123,0.0053,0.9920</t>
-  </si>
-  <si>
-    <t>0.0021,0.0009,0.0001,0.9990</t>
-  </si>
-  <si>
-    <t>0.0004,0.9753,0.7255,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.6707,0.9851,0.0001</t>
-  </si>
-  <si>
-    <t>0.0163,0.3974,0.8150,0.0010</t>
-  </si>
-  <si>
-    <t>0.0016,0.6310,0.8790,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.9866,0.2882,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.9410,0.1918,0.0001</t>
-  </si>
-  <si>
-    <t>0.9750,0.0184,0.0102,0.0008</t>
-  </si>
-  <si>
-    <t>0.9402,0.0811,0.0019,0.0013</t>
-  </si>
-  <si>
-    <t>0.9418,0.0754,0.0066,0.0023</t>
-  </si>
-  <si>
-    <t>0.9885,0.0055,0.0012,0.0010</t>
-  </si>
-  <si>
-    <t>0.9680,0.0368,0.0060,0.0007</t>
-  </si>
-  <si>
-    <t>0.9907,0.0029,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9172,0.1528,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9716,0.0370,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.9942,0.0002,0.0002,0.0023</t>
-  </si>
-  <si>
-    <t>0.9959,0.0010,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9961,0.0016,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9950,0.0009,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9872,0.0076,0.0045,0.0005</t>
-  </si>
-  <si>
-    <t>0.9931,0.0068,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9956,0.0005,0.0003,0.0014</t>
-  </si>
-  <si>
-    <t>0.9896,0.0053,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.0006,0.0103,0.9943,0.0018</t>
-  </si>
-  <si>
-    <t>0.0242,0.1084,0.8799,0.0012</t>
-  </si>
-  <si>
-    <t>0.4861,0.0414,0.4946,0.0219</t>
-  </si>
-  <si>
-    <t>0.2417,0.0061,0.8669,0.0019</t>
-  </si>
-  <si>
-    <t>0.2472,0.8200,0.0046,0.0018</t>
-  </si>
-  <si>
-    <t>0.0230,0.9701,0.0040,0.0007</t>
-  </si>
-  <si>
-    <t>0.0357,0.9442,0.0023,0.0080</t>
-  </si>
-  <si>
-    <t>0.2159,0.8564,0.0012,0.0010</t>
-  </si>
-  <si>
-    <t>0.4871,0.5798,0.0073,0.0213</t>
-  </si>
-  <si>
-    <t>0.0194,0.9693,0.0030,0.0023</t>
-  </si>
-  <si>
-    <t>0.9085,0.1570,0.0025,0.0008</t>
-  </si>
-  <si>
-    <t>0.7145,0.0681,0.2112,0.0271</t>
-  </si>
-  <si>
-    <t>0.6642,0.0093,0.4137,0.0084</t>
-  </si>
-  <si>
-    <t>0.2380,0.4511,0.2480,0.0645</t>
-  </si>
-  <si>
-    <t>0.2674,0.1389,0.6641,0.0169</t>
-  </si>
-  <si>
-    <t>0.0628,0.5974,0.0461,0.7555</t>
-  </si>
-  <si>
-    <t>0.0004,0.9963,0.0184,0.0003</t>
-  </si>
-  <si>
-    <t>0.0029,0.9807,0.1090,0.0059</t>
-  </si>
-  <si>
-    <t>0.0098,0.9723,0.0074,0.0137</t>
-  </si>
-  <si>
-    <t>0.0001,0.9722,0.8324,0.0002</t>
-  </si>
-  <si>
-    <t>0.0048,0.9910,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.8899,0.1583,0.0094,0.0018</t>
-  </si>
-  <si>
-    <t>0.2121,0.8318,0.0013,0.0027</t>
-  </si>
-  <si>
-    <t>0.9894,0.0045,0.0036,0.0004</t>
-  </si>
-  <si>
-    <t>0.9701,0.0096,0.0009,0.0057</t>
-  </si>
-  <si>
-    <t>0.9751,0.0079,0.0028,0.0043</t>
-  </si>
-  <si>
-    <t>0.9612,0.0431,0.0053,0.0004</t>
-  </si>
-  <si>
-    <t>0.9898,0.0018,0.0027,0.0016</t>
-  </si>
-  <si>
-    <t>0.9881,0.0101,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.9191,0.0393,0.0148,0.0139</t>
-  </si>
-  <si>
-    <t>0.9365,0.0295,0.0399,0.0045</t>
-  </si>
-  <si>
-    <t>0.0008,0.8671,0.9669,0.0003</t>
-  </si>
-  <si>
-    <t>0.0018,0.7703,0.9043,0.0003</t>
-  </si>
-  <si>
-    <t>0.0092,0.3459,0.9028,0.0021</t>
-  </si>
-  <si>
-    <t>0.0147,0.4812,0.7756,0.0015</t>
-  </si>
-  <si>
-    <t>0.3571,0.0647,0.4594,0.2076</t>
-  </si>
-  <si>
-    <t>0.8195,0.0341,0.0785,0.0351</t>
-  </si>
-  <si>
-    <t>0.7240,0.0122,0.4201,0.0037</t>
-  </si>
-  <si>
-    <t>0.5759,0.2697,0.1797,0.0156</t>
-  </si>
-  <si>
-    <t>0.0536,0.0083,0.0057,0.9739</t>
-  </si>
-  <si>
-    <t>0.0007,0.0010,0.0007,0.9991</t>
-  </si>
-  <si>
-    <t>0.0006,0.0686,0.0034,0.9966</t>
-  </si>
-  <si>
-    <t>0.0269,0.0150,0.0070,0.9816</t>
-  </si>
-  <si>
-    <t>0.0002,0.8729,0.9743,0.0002</t>
-  </si>
-  <si>
-    <t>0.8776,0.1066,0.0523,0.0052</t>
-  </si>
-  <si>
-    <t>0.6881,0.4551,0.0048,0.0023</t>
-  </si>
-  <si>
-    <t>0.9625,0.0128,0.0048,0.0082</t>
-  </si>
-  <si>
-    <t>0.5327,0.6334,0.0061,0.0005</t>
-  </si>
-  <si>
-    <t>0.9232,0.0320,0.0067,0.0167</t>
-  </si>
-  <si>
-    <t>0.4745,0.0031,0.0012,0.7426</t>
-  </si>
-  <si>
-    <t>0.9484,0.0194,0.0020,0.0129</t>
-  </si>
-  <si>
-    <t>0.0008,0.3773,0.9417,0.0172</t>
-  </si>
-  <si>
-    <t>0.6147,0.0038,0.0027,0.5436</t>
-  </si>
-  <si>
-    <t>0.8190,0.0075,0.0015,0.1976</t>
-  </si>
-  <si>
-    <t>0.3357,0.6753,0.0193,0.0090</t>
-  </si>
-  <si>
-    <t>0.8744,0.0746,0.0049,0.0122</t>
-  </si>
-  <si>
-    <t>0.9487,0.0170,0.0093,0.0044</t>
-  </si>
-  <si>
-    <t>0.5178,0.2741,0.0272,0.1373</t>
-  </si>
-  <si>
-    <t>0.6237,0.3895,0.0441,0.0314</t>
-  </si>
-  <si>
-    <t>0.8742,0.1040,0.0302,0.0052</t>
-  </si>
-  <si>
-    <t>0.9859,0.0037,0.0004,0.0025</t>
-  </si>
-  <si>
-    <t>0.9707,0.0116,0.0045,0.0050</t>
-  </si>
-  <si>
-    <t>0.9888,0.0052,0.0011,0.0008</t>
-  </si>
-  <si>
-    <t>0.9776,0.0027,0.0047,0.0058</t>
-  </si>
-  <si>
-    <t>0.9649,0.0138,0.0047,0.0060</t>
-  </si>
-  <si>
-    <t>0.9665,0.0262,0.0053,0.0022</t>
-  </si>
-  <si>
-    <t>0.9814,0.0095,0.0084,0.0008</t>
-  </si>
-  <si>
-    <t>0.9889,0.0011,0.0001,0.0045</t>
-  </si>
-  <si>
-    <t>0.7357,0.3658,0.0098,0.0107</t>
-  </si>
-  <si>
-    <t>0.1083,0.8838,0.0145,0.0006</t>
-  </si>
-  <si>
-    <t>0.5339,0.5908,0.0076,0.0008</t>
-  </si>
-  <si>
-    <t>0.0566,0.0803,0.9256,0.0037</t>
-  </si>
-  <si>
-    <t>0.7593,0.3797,0.0048,0.0004</t>
-  </si>
-  <si>
-    <t>0.8574,0.1647,0.0085,0.0042</t>
-  </si>
-  <si>
-    <t>0.8969,0.1164,0.0089,0.0005</t>
-  </si>
-  <si>
-    <t>0.9543,0.0367,0.0070,0.0028</t>
-  </si>
-  <si>
-    <t>0.0011,0.0122,0.9965,0.0004</t>
-  </si>
-  <si>
-    <t>0.8973,0.0991,0.0162,0.0051</t>
-  </si>
-  <si>
-    <t>0.0020,0.0010,0.9968,0.0004</t>
-  </si>
-  <si>
-    <t>0.0036,0.2088,0.9773,0.0014</t>
-  </si>
-  <si>
-    <t>0.0027,0.0130,0.9863,0.0050</t>
-  </si>
-  <si>
-    <t>0.0044,0.0822,0.9853,0.0010</t>
-  </si>
-  <si>
-    <t>0.0019,0.0617,0.9888,0.0015</t>
-  </si>
-  <si>
-    <t>0.0067,0.0015,0.9934,0.0003</t>
-  </si>
-  <si>
-    <t>0.0090,0.0061,0.9913,0.0004</t>
-  </si>
-  <si>
-    <t>0.1684,0.5599,0.2296,0.0186</t>
-  </si>
-  <si>
-    <t>0.1654,0.0063,0.9149,0.0005</t>
-  </si>
-  <si>
-    <t>0.5601,0.2419,0.2188,0.0165</t>
-  </si>
-  <si>
-    <t>0.1330,0.4917,0.2619,0.0042</t>
-  </si>
-  <si>
-    <t>0.0146,0.8487,0.2959,0.0024</t>
-  </si>
-  <si>
-    <t>0.5392,0.0393,0.4863,0.0062</t>
-  </si>
-  <si>
-    <t>0.3766,0.0795,0.5846,0.0340</t>
-  </si>
-  <si>
-    <t>0.4218,0.2550,0.3080,0.0112</t>
-  </si>
-  <si>
-    <t>0.7943,0.2614,0.0092,0.0006</t>
-  </si>
-  <si>
-    <t>0.6317,0.5813,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9150,0.1084,0.0055,0.0020</t>
-  </si>
-  <si>
-    <t>0.9273,0.1123,0.0045,0.0006</t>
-  </si>
-  <si>
-    <t>0.9285,0.1079,0.0052,0.0004</t>
-  </si>
-  <si>
-    <t>0.6026,0.0367,0.4224,0.0109</t>
-  </si>
-  <si>
-    <t>0.7935,0.0232,0.2387,0.0081</t>
-  </si>
-  <si>
-    <t>0.6147,0.1504,0.2381,0.0228</t>
-  </si>
-  <si>
-    <t>0.5311,0.0826,0.3943,0.0317</t>
-  </si>
-  <si>
-    <t>0.7417,0.0147,0.2466,0.0462</t>
-  </si>
-  <si>
-    <t>0.0745,0.4430,0.3989,0.1745</t>
-  </si>
-  <si>
-    <t>0.0124,0.2042,0.9291,0.0073</t>
-  </si>
-  <si>
-    <t>0.0748,0.3037,0.8065,0.0100</t>
-  </si>
-  <si>
-    <t>0.0461,0.1004,0.9260,0.0031</t>
-  </si>
-  <si>
-    <t>0.0059,0.1072,0.9525,0.0028</t>
-  </si>
-  <si>
-    <t>0.9865,0.0049,0.0024,0.0018</t>
-  </si>
-  <si>
-    <t>0.9682,0.0381,0.0034,0.0009</t>
-  </si>
-  <si>
-    <t>0.9616,0.0369,0.0086,0.0007</t>
-  </si>
-  <si>
-    <t>0.9936,0.0029,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9825,0.0174,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9865,0.0213,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9935,0.0005,0.0001,0.0020</t>
-  </si>
-  <si>
-    <t>0.9108,0.0994,0.0097,0.0028</t>
-  </si>
-  <si>
-    <t>0.0143,0.0167,0.9841,0.0007</t>
-  </si>
-  <si>
-    <t>0.2025,0.3807,0.4105,0.0023</t>
-  </si>
-  <si>
-    <t>0.9425,0.0309,0.0217,0.0030</t>
-  </si>
-  <si>
-    <t>0.0049,0.0828,0.9726,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0006,0.9972,0.0012</t>
-  </si>
-  <si>
-    <t>0.0040,0.0177,0.9845,0.0023</t>
-  </si>
-  <si>
-    <t>0.0023,0.0053,0.9920,0.0014</t>
-  </si>
-  <si>
-    <t>0.1192,0.0907,0.7837,0.0047</t>
-  </si>
-  <si>
-    <t>0.0003,0.0021,0.9979,0.0003</t>
-  </si>
-  <si>
-    <t>0.0092,0.0137,0.9776,0.0052</t>
-  </si>
-  <si>
-    <t>0.1581,0.6125,0.2206,0.0444</t>
-  </si>
-  <si>
-    <t>0.5896,0.0471,0.3689,0.0446</t>
-  </si>
-  <si>
-    <t>0.0948,0.0042,0.9245,0.0061</t>
-  </si>
-  <si>
-    <t>0.3771,0.0012,0.1591,0.3202</t>
-  </si>
-  <si>
-    <t>0.9766,0.0218,0.0066,0.0006</t>
-  </si>
-  <si>
-    <t>0.9694,0.0152,0.0133,0.0017</t>
-  </si>
-  <si>
-    <t>0.9943,0.0015,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9731,0.0156,0.0060,0.0030</t>
-  </si>
-  <si>
-    <t>0.9365,0.0207,0.0010,0.0140</t>
-  </si>
-  <si>
-    <t>0.9804,0.0165,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.9883,0.0038,0.0015,0.0015</t>
-  </si>
-  <si>
-    <t>0.9853,0.0140,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.0282,0.3491,0.8273,0.0044</t>
-  </si>
-  <si>
-    <t>0.0025,0.0243,0.9762,0.0049</t>
-  </si>
-  <si>
-    <t>0.0164,0.0848,0.9406,0.0086</t>
-  </si>
-  <si>
-    <t>0.0408,0.0292,0.9323,0.0059</t>
-  </si>
-  <si>
-    <t>0.0103,0.0056,0.9872,0.0015</t>
-  </si>
-  <si>
-    <t>0.1170,0.0128,0.6417,0.2964</t>
-  </si>
-  <si>
-    <t>0.0687,0.0579,0.8727,0.0013</t>
-  </si>
-  <si>
-    <t>0.0437,0.1374,0.9057,0.0181</t>
-  </si>
-  <si>
-    <t>0.6694,0.0072,0.0063,0.4671</t>
-  </si>
-  <si>
-    <t>0.0113,0.0654,0.0141,0.9813</t>
-  </si>
-  <si>
-    <t>0.1342,0.0017,0.0020,0.9602</t>
-  </si>
-  <si>
-    <t>0.0025,0.0006,0.0064,0.9962</t>
-  </si>
-  <si>
-    <t>0.0083,0.0003,0.0005,0.9960</t>
-  </si>
-  <si>
-    <t>0.3033,0.1283,0.0165,0.7206</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.3816,0.0100,0.0201,0.7245</t>
+  </si>
+  <si>
+    <t>0.0037,0.0054,0.0009,0.9970</t>
+  </si>
+  <si>
+    <t>0.4307,0.0506,0.1096,0.5697</t>
+  </si>
+  <si>
+    <t>0.0297,0.1666,0.0053,0.9601</t>
+  </si>
+  <si>
+    <t>0.9950,0.0004,0.0000,0.0018</t>
+  </si>
+  <si>
+    <t>0.9900,0.0107,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9791,0.0230,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.9903,0.0028,0.0007,0.0015</t>
+  </si>
+  <si>
+    <t>0.9760,0.0223,0.0018,0.0019</t>
+  </si>
+  <si>
+    <t>0.9881,0.0178,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0009,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9958,0.0014,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.7655,0.0354,0.2060,0.0242</t>
+  </si>
+  <si>
+    <t>0.2271,0.0349,0.8223,0.0010</t>
+  </si>
+  <si>
+    <t>0.3710,0.0092,0.8009,0.0010</t>
+  </si>
+  <si>
+    <t>0.1275,0.0583,0.8046,0.0045</t>
+  </si>
+  <si>
+    <t>0.6766,0.1028,0.2319,0.0353</t>
+  </si>
+  <si>
+    <t>0.0336,0.9606,0.0049,0.0016</t>
+  </si>
+  <si>
+    <t>0.3136,0.8521,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.8499,0.2803,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0279,0.9708,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.0048,0.9920,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.5901,0.0117,0.4429,0.0285</t>
+  </si>
+  <si>
+    <t>0.2705,0.2090,0.5223,0.1273</t>
+  </si>
+  <si>
+    <t>0.0238,0.0131,0.9568,0.0091</t>
+  </si>
+  <si>
+    <t>0.1633,0.0208,0.8232,0.0187</t>
+  </si>
+  <si>
+    <t>0.0146,0.0102,0.9719,0.0053</t>
+  </si>
+  <si>
+    <t>0.0290,0.0069,0.9588,0.0045</t>
+  </si>
+  <si>
+    <t>0.0054,0.0026,0.9851,0.0047</t>
+  </si>
+  <si>
+    <t>0.3311,0.7757,0.0068,0.0020</t>
+  </si>
+  <si>
+    <t>0.4497,0.4033,0.2857,0.0352</t>
+  </si>
+  <si>
+    <t>0.0125,0.0076,0.9745,0.0031</t>
+  </si>
+  <si>
+    <t>0.0537,0.2871,0.7501,0.0021</t>
+  </si>
+  <si>
+    <t>0.4986,0.5093,0.0587,0.0241</t>
+  </si>
+  <si>
+    <t>0.0740,0.2880,0.8279,0.0048</t>
+  </si>
+  <si>
+    <t>0.7484,0.2664,0.0276,0.0020</t>
+  </si>
+  <si>
+    <t>0.0296,0.9588,0.0972,0.0014</t>
+  </si>
+  <si>
+    <t>0.0939,0.7251,0.2807,0.0402</t>
+  </si>
+  <si>
+    <t>0.0293,0.0277,0.9251,0.0403</t>
+  </si>
+  <si>
+    <t>0.0166,0.6934,0.7757,0.0067</t>
+  </si>
+  <si>
+    <t>0.1675,0.0845,0.2719,0.6505</t>
+  </si>
+  <si>
+    <t>0.0061,0.1295,0.9708,0.0017</t>
+  </si>
+  <si>
+    <t>0.0095,0.9224,0.1724,0.0009</t>
+  </si>
+  <si>
+    <t>0.0060,0.0939,0.9613,0.0027</t>
+  </si>
+  <si>
+    <t>0.0279,0.8352,0.0220,0.4551</t>
+  </si>
+  <si>
+    <t>0.0143,0.9559,0.0195,0.0253</t>
+  </si>
+  <si>
+    <t>0.0004,0.9874,0.2769,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9931,0.0196,0.0068</t>
+  </si>
+  <si>
+    <t>0.0005,0.5274,0.9840,0.0009</t>
+  </si>
+  <si>
+    <t>0.0012,0.1262,0.9924,0.0006</t>
+  </si>
+  <si>
+    <t>0.3084,0.0307,0.6977,0.0171</t>
+  </si>
+  <si>
+    <t>0.0078,0.0009,0.9860,0.0040</t>
+  </si>
+  <si>
+    <t>0.0008,0.0108,0.9962,0.0003</t>
+  </si>
+  <si>
+    <t>0.0028,0.0301,0.9866,0.0013</t>
+  </si>
+  <si>
+    <t>0.7511,0.3235,0.0050,0.0031</t>
+  </si>
+  <si>
+    <t>0.9601,0.0170,0.0010,0.0078</t>
+  </si>
+  <si>
+    <t>0.8759,0.1856,0.0019,0.0012</t>
+  </si>
+  <si>
+    <t>0.0054,0.0134,0.9885,0.0010</t>
+  </si>
+  <si>
+    <t>0.9524,0.0450,0.0052,0.0028</t>
+  </si>
+  <si>
+    <t>0.9775,0.0146,0.0023,0.0017</t>
+  </si>
+  <si>
+    <t>0.9285,0.1141,0.0036,0.0007</t>
+  </si>
+  <si>
+    <t>0.0013,0.5498,0.9831,0.0010</t>
+  </si>
+  <si>
+    <t>0.0015,0.0252,0.9782,0.0095</t>
+  </si>
+  <si>
+    <t>0.0159,0.0283,0.9674,0.0037</t>
+  </si>
+  <si>
+    <t>0.0001,0.8888,0.9895,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0041,0.9947,0.0027</t>
+  </si>
+  <si>
+    <t>0.0082,0.8194,0.6377,0.0012</t>
+  </si>
+  <si>
+    <t>0.0279,0.9698,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.8864,0.0526,0.0459,0.0076</t>
+  </si>
+  <si>
+    <t>0.8291,0.0917,0.0281,0.0187</t>
+  </si>
+  <si>
+    <t>0.0988,0.0972,0.8105,0.0024</t>
+  </si>
+  <si>
+    <t>0.0015,0.9559,0.3097,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.9676,0.6711,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9704,0.4199,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9652,0.9444,0.0000</t>
+  </si>
+  <si>
+    <t>0.0630,0.0043,0.0490,0.9347</t>
+  </si>
+  <si>
+    <t>0.0062,0.0027,0.0046,0.9939</t>
+  </si>
+  <si>
+    <t>0.0005,0.0076,0.0002,0.9991</t>
+  </si>
+  <si>
+    <t>0.0275,0.0086,0.0169,0.9759</t>
+  </si>
+  <si>
+    <t>0.0249,0.0097,0.0028,0.9867</t>
+  </si>
+  <si>
+    <t>0.0024,0.0032,0.0012,0.9979</t>
+  </si>
+  <si>
+    <t>0.0005,0.9816,0.5934,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.7479,0.9858,0.0003</t>
+  </si>
+  <si>
+    <t>0.0097,0.4245,0.9147,0.0037</t>
+  </si>
+  <si>
+    <t>0.0030,0.5221,0.9328,0.0005</t>
+  </si>
+  <si>
+    <t>0.0013,0.9684,0.2478,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.6408,0.8926,0.0008</t>
+  </si>
+  <si>
+    <t>0.9847,0.0120,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.9225,0.0612,0.0212,0.0007</t>
+  </si>
+  <si>
+    <t>0.9847,0.0153,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9824,0.0194,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9746,0.0078,0.0009,0.0049</t>
+  </si>
+  <si>
+    <t>0.9942,0.0017,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9745,0.0444,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9903,0.0130,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9922,0.0033,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9938,0.0066,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9937,0.0009,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.9940,0.0009,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9976,0.0011,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9866,0.0107,0.0022,0.0005</t>
+  </si>
+  <si>
+    <t>0.9934,0.0007,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.9938,0.0016,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.0013,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.1777,0.0312,0.8562,0.0048</t>
+  </si>
+  <si>
+    <t>0.7170,0.0092,0.1154,0.1069</t>
+  </si>
+  <si>
+    <t>0.0205,0.0101,0.9616,0.0023</t>
+  </si>
+  <si>
+    <t>0.0287,0.9556,0.0083,0.0014</t>
+  </si>
+  <si>
+    <t>0.0838,0.9297,0.0054,0.0008</t>
+  </si>
+  <si>
+    <t>0.0258,0.9710,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.2530,0.8395,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.0025,0.9926,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.0180,0.9796,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.7687,0.3017,0.0123,0.0019</t>
+  </si>
+  <si>
+    <t>0.6537,0.1233,0.1605,0.0353</t>
+  </si>
+  <si>
+    <t>0.1503,0.0147,0.8848,0.0028</t>
+  </si>
+  <si>
+    <t>0.7381,0.0817,0.0829,0.0469</t>
+  </si>
+  <si>
+    <t>0.4128,0.2571,0.3261,0.0496</t>
+  </si>
+  <si>
+    <t>0.3356,0.2619,0.3029,0.4205</t>
+  </si>
+  <si>
+    <t>0.0019,0.9906,0.0240,0.0022</t>
+  </si>
+  <si>
+    <t>0.0005,0.9882,0.0183,0.0431</t>
+  </si>
+  <si>
+    <t>0.0265,0.9037,0.0261,0.1238</t>
+  </si>
+  <si>
+    <t>0.0002,0.9833,0.7516,0.0002</t>
+  </si>
+  <si>
+    <t>0.0048,0.9874,0.0276,0.0005</t>
+  </si>
+  <si>
+    <t>0.7431,0.2751,0.0589,0.0096</t>
+  </si>
+  <si>
+    <t>0.1345,0.8855,0.0058,0.0017</t>
+  </si>
+  <si>
+    <t>0.9904,0.0036,0.0024,0.0010</t>
+  </si>
+  <si>
+    <t>0.9931,0.0017,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9744,0.0031,0.0010,0.0121</t>
+  </si>
+  <si>
+    <t>0.9686,0.0049,0.0004,0.0093</t>
+  </si>
+  <si>
+    <t>0.9905,0.0027,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9829,0.0316,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9690,0.0077,0.0273,0.0021</t>
+  </si>
+  <si>
+    <t>0.9833,0.0093,0.0016,0.0019</t>
+  </si>
+  <si>
+    <t>0.0022,0.5118,0.9662,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.8839,0.9739,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0423,0.9912,0.0012</t>
+  </si>
+  <si>
+    <t>0.0042,0.5981,0.8598,0.0004</t>
+  </si>
+  <si>
+    <t>0.5253,0.0926,0.1899,0.2947</t>
+  </si>
+  <si>
+    <t>0.7880,0.0228,0.1382,0.0419</t>
+  </si>
+  <si>
+    <t>0.2108,0.0069,0.8758,0.0054</t>
+  </si>
+  <si>
+    <t>0.6926,0.0183,0.3021,0.0360</t>
+  </si>
+  <si>
+    <t>0.0806,0.0054,0.0020,0.9705</t>
+  </si>
+  <si>
+    <t>0.0002,0.0092,0.0021,0.9992</t>
+  </si>
+  <si>
+    <t>0.0054,0.0202,0.0024,0.9944</t>
+  </si>
+  <si>
+    <t>0.0019,0.0009,0.0023,0.9979</t>
+  </si>
+  <si>
+    <t>0.0080,0.8507,0.7027,0.0030</t>
+  </si>
+  <si>
+    <t>0.9249,0.1290,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.2452,0.7981,0.0060,0.0023</t>
+  </si>
+  <si>
+    <t>0.9728,0.0066,0.0031,0.0068</t>
+  </si>
+  <si>
+    <t>0.3859,0.7012,0.0062,0.0032</t>
+  </si>
+  <si>
+    <t>0.9762,0.0060,0.0013,0.0042</t>
+  </si>
+  <si>
+    <t>0.9036,0.0104,0.0096,0.0583</t>
+  </si>
+  <si>
+    <t>0.9519,0.0348,0.0154,0.0017</t>
+  </si>
+  <si>
+    <t>0.0002,0.2759,0.9316,0.0590</t>
+  </si>
+  <si>
+    <t>0.5414,0.0055,0.0586,0.3975</t>
+  </si>
+  <si>
+    <t>0.9347,0.0119,0.0056,0.0239</t>
+  </si>
+  <si>
+    <t>0.7253,0.3498,0.0078,0.0082</t>
+  </si>
+  <si>
+    <t>0.8369,0.1141,0.0070,0.0155</t>
+  </si>
+  <si>
+    <t>0.9016,0.0628,0.0113,0.0061</t>
+  </si>
+  <si>
+    <t>0.6252,0.1736,0.2403,0.0145</t>
+  </si>
+  <si>
+    <t>0.7820,0.2408,0.0276,0.0062</t>
+  </si>
+  <si>
+    <t>0.4819,0.6578,0.0090,0.0047</t>
+  </si>
+  <si>
+    <t>0.9814,0.0073,0.0036,0.0017</t>
+  </si>
+  <si>
+    <t>0.9557,0.0286,0.0200,0.0019</t>
+  </si>
+  <si>
+    <t>0.9817,0.0060,0.0042,0.0032</t>
+  </si>
+  <si>
+    <t>0.9683,0.0034,0.0031,0.0170</t>
+  </si>
+  <si>
+    <t>0.9360,0.0354,0.0356,0.0031</t>
+  </si>
+  <si>
+    <t>0.9802,0.0125,0.0061,0.0013</t>
+  </si>
+  <si>
+    <t>0.9725,0.0095,0.0026,0.0056</t>
+  </si>
+  <si>
+    <t>0.9769,0.0033,0.0031,0.0091</t>
+  </si>
+  <si>
+    <t>0.5183,0.4619,0.0036,0.0198</t>
+  </si>
+  <si>
+    <t>0.4486,0.6398,0.0165,0.0027</t>
+  </si>
+  <si>
+    <t>0.6388,0.5048,0.0030,0.0013</t>
+  </si>
+  <si>
+    <t>0.2547,0.5097,0.3951,0.0184</t>
+  </si>
+  <si>
+    <t>0.7705,0.2781,0.0024,0.0052</t>
+  </si>
+  <si>
+    <t>0.8917,0.0725,0.0058,0.0117</t>
+  </si>
+  <si>
+    <t>0.8126,0.3755,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9576,0.0258,0.0089,0.0026</t>
+  </si>
+  <si>
+    <t>0.0018,0.0156,0.9929,0.0012</t>
+  </si>
+  <si>
+    <t>0.9648,0.0370,0.0030,0.0011</t>
+  </si>
+  <si>
+    <t>0.0014,0.0170,0.9917,0.0012</t>
+  </si>
+  <si>
+    <t>0.0039,0.3916,0.9558,0.0029</t>
+  </si>
+  <si>
+    <t>0.1003,0.0204,0.9010,0.0077</t>
+  </si>
+  <si>
+    <t>0.0006,0.0201,0.9949,0.0008</t>
+  </si>
+  <si>
+    <t>0.0017,0.1309,0.9851,0.0007</t>
+  </si>
+  <si>
+    <t>0.0071,0.0249,0.9790,0.0010</t>
+  </si>
+  <si>
+    <t>0.0043,0.0255,0.9893,0.0007</t>
+  </si>
+  <si>
+    <t>0.4431,0.0213,0.6509,0.0071</t>
+  </si>
+  <si>
+    <t>0.3544,0.1116,0.6154,0.0107</t>
+  </si>
+  <si>
+    <t>0.7000,0.0100,0.4502,0.0034</t>
+  </si>
+  <si>
+    <t>0.3614,0.0566,0.6378,0.0042</t>
+  </si>
+  <si>
+    <t>0.1072,0.5720,0.2684,0.0122</t>
+  </si>
+  <si>
+    <t>0.0398,0.6576,0.2605,0.0029</t>
+  </si>
+  <si>
+    <t>0.1643,0.5485,0.3551,0.1332</t>
+  </si>
+  <si>
+    <t>0.4241,0.0758,0.5566,0.0060</t>
+  </si>
+  <si>
+    <t>0.8472,0.1687,0.0190,0.0024</t>
+  </si>
+  <si>
+    <t>0.5579,0.5843,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.9474,0.0438,0.0102,0.0036</t>
+  </si>
+  <si>
+    <t>0.9393,0.1126,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.6205,0.5062,0.0197,0.0041</t>
+  </si>
+  <si>
+    <t>0.5429,0.1127,0.4233,0.0196</t>
+  </si>
+  <si>
+    <t>0.7560,0.0646,0.0316,0.0965</t>
+  </si>
+  <si>
+    <t>0.5949,0.0185,0.0863,0.2836</t>
+  </si>
+  <si>
+    <t>0.6033,0.0107,0.5442,0.0049</t>
+  </si>
+  <si>
+    <t>0.5294,0.2937,0.0271,0.0654</t>
+  </si>
+  <si>
+    <t>0.0046,0.0153,0.9741,0.0183</t>
+  </si>
+  <si>
+    <t>0.0379,0.3338,0.8231,0.0439</t>
+  </si>
+  <si>
+    <t>0.0052,0.3240,0.9468,0.0067</t>
+  </si>
+  <si>
+    <t>0.0983,0.0271,0.9016,0.0071</t>
+  </si>
+  <si>
+    <t>0.0363,0.2047,0.8027,0.0397</t>
+  </si>
+  <si>
+    <t>0.9776,0.0241,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9792,0.0169,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9720,0.0170,0.0017,0.0028</t>
+  </si>
+  <si>
+    <t>0.9820,0.0128,0.0023,0.0013</t>
+  </si>
+  <si>
+    <t>0.9787,0.0319,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9836,0.0073,0.0031,0.0022</t>
+  </si>
+  <si>
+    <t>0.9809,0.0071,0.0006,0.0028</t>
+  </si>
+  <si>
+    <t>0.9806,0.0130,0.0020,0.0014</t>
+  </si>
+  <si>
+    <t>0.0637,0.0123,0.9571,0.0009</t>
+  </si>
+  <si>
+    <t>0.0342,0.9124,0.0732,0.0041</t>
+  </si>
+  <si>
+    <t>0.8548,0.0439,0.1339,0.0069</t>
+  </si>
+  <si>
+    <t>0.0094,0.0128,0.9741,0.0053</t>
+  </si>
+  <si>
+    <t>0.0001,0.0025,0.9974,0.0014</t>
+  </si>
+  <si>
+    <t>0.0053,0.2502,0.9427,0.0024</t>
+  </si>
+  <si>
+    <t>0.0002,0.0016,0.9947,0.0040</t>
+  </si>
+  <si>
+    <t>0.0269,0.0127,0.9561,0.0033</t>
+  </si>
+  <si>
+    <t>0.0028,0.0015,0.9953,0.0004</t>
+  </si>
+  <si>
+    <t>0.0193,0.1293,0.9187,0.0042</t>
+  </si>
+  <si>
+    <t>0.1699,0.0814,0.7557,0.0302</t>
+  </si>
+  <si>
+    <t>0.6765,0.0139,0.3648,0.0260</t>
+  </si>
+  <si>
+    <t>0.7430,0.0010,0.5024,0.0022</t>
+  </si>
+  <si>
+    <t>0.8230,0.0092,0.1224,0.0241</t>
+  </si>
+  <si>
+    <t>0.9439,0.0868,0.0048,0.0012</t>
+  </si>
+  <si>
+    <t>0.9703,0.0415,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9927,0.0024,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9825,0.0197,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9781,0.0131,0.0018,0.0025</t>
+  </si>
+  <si>
+    <t>0.9848,0.0206,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9891,0.0092,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9775,0.0132,0.0006,0.0024</t>
+  </si>
+  <si>
+    <t>0.0241,0.0751,0.9256,0.0072</t>
+  </si>
+  <si>
+    <t>0.0038,0.2279,0.9725,0.0002</t>
+  </si>
+  <si>
+    <t>0.0046,0.0924,0.9672,0.0005</t>
+  </si>
+  <si>
+    <t>0.1558,0.0227,0.8360,0.0108</t>
+  </si>
+  <si>
+    <t>0.0009,0.0047,0.9782,0.0415</t>
+  </si>
+  <si>
+    <t>0.3176,0.0189,0.0646,0.7086</t>
+  </si>
+  <si>
+    <t>0.2686,0.0812,0.7039,0.0112</t>
+  </si>
+  <si>
+    <t>0.0080,0.0121,0.8876,0.1668</t>
+  </si>
+  <si>
+    <t>0.8500,0.0012,0.0126,0.1096</t>
+  </si>
+  <si>
+    <t>0.0037,0.2965,0.0034,0.9824</t>
+  </si>
+  <si>
+    <t>0.0934,0.0147,0.0120,0.9487</t>
+  </si>
+  <si>
+    <t>0.0133,0.0001,0.0011,0.9941</t>
+  </si>
+  <si>
+    <t>0.0025,0.0006,0.0008,0.9982</t>
+  </si>
+  <si>
+    <t>0.8406,0.0198,0.0279,0.0614</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1962,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1993,7 @@
         <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,10 +2312,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,10 +2424,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,10 +2508,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,10 +2522,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,10 +2634,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,10 +2886,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,10 +2956,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2998,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3127,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3166,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3572,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3617,7 @@
         <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3715,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,10 +3880,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3922,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4065,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4132,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,10 +4230,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4373,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4653,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,10 +4846,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,10 +5168,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5518,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
